--- a/data/RP_Software_Aprobado.xlsx
+++ b/data/RP_Software_Aprobado.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29421"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC0CF8F2-8C10-43C3-96A3-188BE45AF17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7F4282D-7FA2-4695-BFC9-6088CA8019D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="113">
   <si>
     <t>Inventario de Software por Rol / Puesto</t>
   </si>
@@ -114,31 +114,31 @@
     <t>AutoDesk AutoCAD 2022</t>
   </si>
   <si>
+    <t>Gerencia</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>Mantenimiento</t>
+  </si>
+  <si>
+    <t>Mecanica</t>
+  </si>
+  <si>
+    <t>Exclusividad Windows 10, realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación. Luego de instalación NO ejecutar, llamar a usuario de Sistemas.</t>
+  </si>
+  <si>
+    <t>Produccion</t>
+  </si>
+  <si>
     <t>Coordinacion Ventas</t>
   </si>
   <si>
     <t>Adrian Bouquet</t>
   </si>
   <si>
-    <t>Gerencia CA</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>Mecanica</t>
-  </si>
-  <si>
-    <t>Exclusividad Windows 10, realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación. Luego de instalación NO ejecutar, llamar a usuario de Sistemas.</t>
-  </si>
-  <si>
-    <t>Mantenimiento</t>
-  </si>
-  <si>
-    <t>Produccion</t>
-  </si>
-  <si>
-    <t>Autodesk Inventor 2022</t>
+    <t>AutoDesk Inventor 2022</t>
   </si>
   <si>
     <t>Realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación. Luego de instalación NO ejecutar, llamar a usuario de Sistemas.</t>
@@ -183,15 +183,18 @@
     <t>DWG FastView</t>
   </si>
   <si>
+    <t>Vigilancia</t>
+  </si>
+  <si>
+    <t>Ezviz Studio</t>
+  </si>
+  <si>
     <t>Foxit PDF Reader</t>
   </si>
   <si>
     <t>para visualización, edición y batch print de pdf ordenados</t>
   </si>
   <si>
-    <t>Desarrollador</t>
-  </si>
-  <si>
     <t>Git</t>
   </si>
   <si>
@@ -201,15 +204,18 @@
     <t>Google Drive</t>
   </si>
   <si>
+    <t>Calidad</t>
+  </si>
+  <si>
+    <t>HiLookVision</t>
+  </si>
+  <si>
+    <t>Expedicion</t>
+  </si>
+  <si>
     <t>Coordinacion Produccion</t>
   </si>
   <si>
-    <t>HiLookVision</t>
-  </si>
-  <si>
-    <t>Vigilancia</t>
-  </si>
-  <si>
     <t>Taller</t>
   </si>
   <si>
@@ -225,84 +231,96 @@
     <t>IXON VPN</t>
   </si>
   <si>
+    <t>Electronica</t>
+  </si>
+  <si>
+    <t>Lider de Proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaspersky </t>
+  </si>
+  <si>
+    <t>KeePassXC</t>
+  </si>
+  <si>
+    <t>Krita</t>
+  </si>
+  <si>
+    <t>LibreOffice</t>
+  </si>
+  <si>
+    <t>Macrium Reflect</t>
+  </si>
+  <si>
+    <t>Malwarebytes</t>
+  </si>
+  <si>
+    <t>Medibang Pro Paint</t>
+  </si>
+  <si>
+    <t>Microsoft Office</t>
+  </si>
+  <si>
+    <t>2016 / 2019 / 2021</t>
+  </si>
+  <si>
+    <t>Microsoft OneDrive</t>
+  </si>
+  <si>
+    <t>Microsoft Proyect</t>
+  </si>
+  <si>
+    <t>Franco Raad</t>
+  </si>
+  <si>
+    <t>Mozilla Firefox</t>
+  </si>
+  <si>
+    <t>MySQL</t>
+  </si>
+  <si>
+    <t>Instalar version full.</t>
+  </si>
+  <si>
+    <t>NiceLabel</t>
+  </si>
+  <si>
+    <t>Node.js</t>
+  </si>
+  <si>
+    <t>Notepad++</t>
+  </si>
+  <si>
+    <t>OBS Studio</t>
+  </si>
+  <si>
+    <t>Outlook for Windows</t>
+  </si>
+  <si>
+    <t>Postman</t>
+  </si>
+  <si>
+    <t>PowerToys</t>
+  </si>
+  <si>
+    <t>Proyect Office 2021</t>
+  </si>
+  <si>
+    <t>Mariano Perez</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>3.13 / Reciente</t>
+  </si>
+  <si>
+    <t>Descargar desde Microsoft Store</t>
+  </si>
+  <si>
     <t>Lider Proyecto</t>
   </si>
   <si>
-    <t>Electronica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaspersky </t>
-  </si>
-  <si>
-    <t>KeePassXC</t>
-  </si>
-  <si>
-    <t>Krita</t>
-  </si>
-  <si>
-    <t>Macrium Reflect</t>
-  </si>
-  <si>
-    <t>Malwarebytes</t>
-  </si>
-  <si>
-    <t>Medibang Pro Paint</t>
-  </si>
-  <si>
-    <t>Microsoft Office</t>
-  </si>
-  <si>
-    <t>2016 / 2019 / 2021</t>
-  </si>
-  <si>
-    <t>Microsoft OneDrive</t>
-  </si>
-  <si>
-    <t>Microsoft Proyect</t>
-  </si>
-  <si>
-    <t>Franco Raad</t>
-  </si>
-  <si>
-    <t>Mozilla Firefox</t>
-  </si>
-  <si>
-    <t>MySQL</t>
-  </si>
-  <si>
-    <t>Instalar version full.</t>
-  </si>
-  <si>
-    <t>NiceLabel</t>
-  </si>
-  <si>
-    <t>Node.js</t>
-  </si>
-  <si>
-    <t>Notepad++</t>
-  </si>
-  <si>
-    <t>OBS Studio</t>
-  </si>
-  <si>
-    <t>Postman</t>
-  </si>
-  <si>
-    <t>Proyect Office 2021</t>
-  </si>
-  <si>
-    <t>Mariano Perez</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>3.13 / Reciente</t>
-  </si>
-  <si>
-    <t>Descargar desde Microsoft Store</t>
-  </si>
-  <si>
     <t>Reflect</t>
   </si>
   <si>
@@ -327,12 +345,18 @@
     <t>Desde Microsoft Store</t>
   </si>
   <si>
-    <t>Tia Portal</t>
+    <t>Tia Portal V16</t>
   </si>
   <si>
     <t>V16</t>
   </si>
   <si>
+    <t>Tia Portal V17</t>
+  </si>
+  <si>
+    <t>V17</t>
+  </si>
+  <si>
     <t>UaExpert</t>
   </si>
   <si>
@@ -342,19 +366,10 @@
     <t>VLC Media Player</t>
   </si>
   <si>
-    <t>Whatssap</t>
-  </si>
-  <si>
-    <t>Windows 10 Pro</t>
+    <t>WhatsApp</t>
   </si>
   <si>
     <t>WinRAR</t>
-  </si>
-  <si>
-    <t>Outlook for Windows</t>
-  </si>
-  <si>
-    <t>PowerToys</t>
   </si>
   <si>
     <t>XAMPP</t>
@@ -568,10 +583,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G85" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A2:G85" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G85">
-    <sortCondition ref="C2:C85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G92" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A2:G92" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G92">
+    <sortCondition ref="C2:C92"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Area / Rol" dataDxfId="6"/>
@@ -762,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
@@ -916,22 +931,18 @@
     </row>
     <row r="10" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="1">
         <v>2022</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -948,13 +959,13 @@
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -968,12 +979,12 @@
         <v>10</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -986,30 +997,34 @@
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="14" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="1">
         <v>2022</v>
       </c>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" ht="15.75">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>34</v>
@@ -1026,7 +1041,7 @@
     </row>
     <row r="16" spans="1:7" ht="15.75">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>34</v>
@@ -1107,7 +1122,7 @@
     </row>
     <row r="22" spans="1:7" ht="15.75">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>42</v>
@@ -1135,7 +1150,7 @@
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>44</v>
@@ -1155,7 +1170,7 @@
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>48</v>
@@ -1163,7 +1178,7 @@
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>48</v>
@@ -1179,54 +1194,48 @@
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>53</v>
@@ -1237,92 +1246,83 @@
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="F33" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1">
       <c r="A35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>61</v>
@@ -1333,23 +1333,23 @@
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -1358,13 +1358,10 @@
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>10</v>
@@ -1372,13 +1369,10 @@
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>10</v>
@@ -1386,13 +1380,13 @@
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>10</v>
@@ -1400,10 +1394,10 @@
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1">
       <c r="A47" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>10</v>
@@ -1411,40 +1405,46 @@
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1">
       <c r="A48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1">
+      <c r="A49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15" customHeight="1">
+      <c r="A50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15" customHeight="1">
+      <c r="A51" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="15" customHeight="1">
-      <c r="A49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15" customHeight="1">
-      <c r="A50" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" customHeight="1">
-      <c r="A51" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>67</v>
@@ -1453,7 +1453,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" customHeight="1">
+    <row r="52" spans="1:6" ht="15" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>8</v>
       </c>
@@ -1464,154 +1464,142 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" customHeight="1">
+    <row r="53" spans="1:6" ht="15" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="15" customHeight="1">
+      <c r="F53" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="15" customHeight="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15" customHeight="1">
       <c r="A55" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15" customHeight="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15" customHeight="1">
+      <c r="A57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15" customHeight="1">
+      <c r="A58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15" customHeight="1">
-      <c r="A57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D57" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15" customHeight="1">
-      <c r="A58" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D58" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15" customHeight="1">
+    <row r="59" spans="1:6" ht="15" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15" customHeight="1">
+      <c r="A60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" customHeight="1">
-      <c r="A60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C60" s="1" t="s">
+    </row>
+    <row r="61" spans="1:6" ht="15" customHeight="1">
+      <c r="A61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" s="1" t="s">
+      <c r="D61" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15" customHeight="1">
+      <c r="A62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="15" customHeight="1">
-      <c r="A61" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15" customHeight="1">
-      <c r="A62" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="F62" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15" customHeight="1">
+    <row r="63" spans="1:6" ht="15" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="15" customHeight="1">
+        <v>79</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1">
@@ -1619,15 +1607,18 @@
         <v>20</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>82</v>
@@ -1638,117 +1629,78 @@
     </row>
     <row r="67" spans="1:7" ht="15" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D69" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E69" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>10</v>
@@ -1759,27 +1711,18 @@
         <v>8</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="D76" s="1">
+        <v>2021</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>90</v>
@@ -1792,98 +1735,217 @@
       <c r="A77" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="C77" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="B80" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="C80" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="15" customHeight="1">
+    <row r="81" spans="1:7" ht="15" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15" customHeight="1">
+    <row r="82" spans="1:7" ht="15" customHeight="1">
       <c r="A82" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15" customHeight="1">
+      <c r="A83" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="15" customHeight="1">
-      <c r="A83" s="1" t="s">
+    </row>
+    <row r="84" spans="1:7" ht="15" customHeight="1">
+      <c r="A84" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15" customHeight="1">
+      <c r="A85" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15" customHeight="1">
+      <c r="A86" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15" customHeight="1">
+      <c r="A87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15" customHeight="1">
+      <c r="A88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15" customHeight="1">
+      <c r="A89" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="15" customHeight="1">
-      <c r="A84" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15" customHeight="1">
+      <c r="A90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15" customHeight="1">
+      <c r="A91" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="15" customHeight="1">
-      <c r="A85" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F85" s="1" t="s">
+      <c r="C91" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15" customHeight="1">
+      <c r="A92" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/data/RP_Software_Aprobado.xlsx
+++ b/data/RP_Software_Aprobado.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29421"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7F4282D-7FA2-4695-BFC9-6088CA8019D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49252AE1-750B-4DC3-BFCE-F7CFFBF08E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="127">
   <si>
     <t>Inventario de Software por Rol / Puesto</t>
   </si>
@@ -114,30 +114,30 @@
     <t>AutoDesk AutoCAD 2022</t>
   </si>
   <si>
+    <t>Coordinacion Ventas</t>
+  </si>
+  <si>
+    <t>Adrian Bouquet</t>
+  </si>
+  <si>
     <t>Gerencia</t>
   </si>
   <si>
     <t>CA</t>
   </si>
   <si>
+    <t>Mecanica</t>
+  </si>
+  <si>
+    <t>Exclusividad Windows 10, realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación. Luego de instalación NO ejecutar, llamar a usuario de Sistemas.</t>
+  </si>
+  <si>
     <t>Mantenimiento</t>
   </si>
   <si>
-    <t>Mecanica</t>
-  </si>
-  <si>
-    <t>Exclusividad Windows 10, realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación. Luego de instalación NO ejecutar, llamar a usuario de Sistemas.</t>
-  </si>
-  <si>
     <t>Produccion</t>
   </si>
   <si>
-    <t>Coordinacion Ventas</t>
-  </si>
-  <si>
-    <t>Adrian Bouquet</t>
-  </si>
-  <si>
     <t>AutoDesk Inventor 2022</t>
   </si>
   <si>
@@ -189,6 +189,12 @@
     <t>Ezviz Studio</t>
   </si>
   <si>
+    <t>Electronica</t>
+  </si>
+  <si>
+    <t>EcoStruxure Machine Expert - Basic</t>
+  </si>
+  <si>
     <t>Foxit PDF Reader</t>
   </si>
   <si>
@@ -204,18 +210,18 @@
     <t>Google Drive</t>
   </si>
   <si>
+    <t>Coordinacion Produccion</t>
+  </si>
+  <si>
+    <t>HiLookVision</t>
+  </si>
+  <si>
     <t>Calidad</t>
   </si>
   <si>
-    <t>HiLookVision</t>
-  </si>
-  <si>
     <t>Expedicion</t>
   </si>
   <si>
-    <t>Coordinacion Produccion</t>
-  </si>
-  <si>
     <t>Taller</t>
   </si>
   <si>
@@ -231,9 +237,6 @@
     <t>IXON VPN</t>
   </si>
   <si>
-    <t>Electronica</t>
-  </si>
-  <si>
     <t>Lider de Proyecto</t>
   </si>
   <si>
@@ -246,9 +249,15 @@
     <t>Krita</t>
   </si>
   <si>
+    <t>KUKA Engineering Tools</t>
+  </si>
+  <si>
     <t>LibreOffice</t>
   </si>
   <si>
+    <t>Logi Options+</t>
+  </si>
+  <si>
     <t>Macrium Reflect</t>
   </si>
   <si>
@@ -336,6 +345,15 @@
     <t>S.I.Ap.</t>
   </si>
   <si>
+    <t>Siemens OPCUA v17</t>
+  </si>
+  <si>
+    <t>SIMATIC V17</t>
+  </si>
+  <si>
+    <t>Smart Connect</t>
+  </si>
+  <si>
     <t>Seclore</t>
   </si>
   <si>
@@ -345,6 +363,18 @@
     <t>Desde Microsoft Store</t>
   </si>
   <si>
+    <t>ISPSoft</t>
+  </si>
+  <si>
+    <t>TD Keypad Designer</t>
+  </si>
+  <si>
+    <t>TxConfig</t>
+  </si>
+  <si>
+    <t>TxConfig II</t>
+  </si>
+  <si>
     <t>Tia Portal V16</t>
   </si>
   <si>
@@ -360,13 +390,25 @@
     <t>UaExpert</t>
   </si>
   <si>
+    <t>UltraVNC</t>
+  </si>
+  <si>
+    <t>Vijeo Designer</t>
+  </si>
+  <si>
     <t>Visual Studio Code</t>
   </si>
   <si>
     <t>VLC Media Player</t>
   </si>
   <si>
+    <t>Virtual COM</t>
+  </si>
+  <si>
     <t>WhatsApp</t>
+  </si>
+  <si>
+    <t>WorkVisual</t>
   </si>
   <si>
     <t>WinRAR</t>
@@ -583,10 +625,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G92" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A2:G92" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G92">
-    <sortCondition ref="C2:C92"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G107" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A2:G107" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G107">
+    <sortCondition ref="C2:C107"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Area / Rol" dataDxfId="6"/>
@@ -777,12 +819,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="37.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="23.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="94.140625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="8.85546875" style="1"/>
@@ -931,18 +973,22 @@
     </row>
     <row r="10" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="1">
         <v>2022</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -959,13 +1005,13 @@
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -979,12 +1025,12 @@
         <v>10</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -997,34 +1043,30 @@
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="1">
         <v>2022</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="15.75">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>34</v>
@@ -1041,7 +1083,7 @@
     </row>
     <row r="16" spans="1:7" ht="15.75">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>34</v>
@@ -1122,7 +1164,7 @@
     </row>
     <row r="22" spans="1:7" ht="15.75">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>42</v>
@@ -1150,7 +1192,7 @@
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>44</v>
@@ -1170,7 +1212,7 @@
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>48</v>
@@ -1178,7 +1220,7 @@
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>48</v>
@@ -1202,35 +1244,35 @@
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1">
@@ -1240,16 +1282,13 @@
       <c r="C32" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>10</v>
@@ -1257,18 +1296,21 @@
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>57</v>
@@ -1276,21 +1318,21 @@
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1">
       <c r="A36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1">
@@ -1298,7 +1340,7 @@
         <v>20</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1">
@@ -1306,51 +1348,51 @@
         <v>60</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1">
       <c r="A41" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>10</v>
@@ -1363,16 +1405,13 @@
       <c r="C44" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>10</v>
@@ -1380,13 +1419,10 @@
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>10</v>
@@ -1394,10 +1430,13 @@
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>65</v>
+        <v>23</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>10</v>
@@ -1405,13 +1444,13 @@
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>10</v>
@@ -1419,13 +1458,13 @@
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>10</v>
@@ -1436,7 +1475,7 @@
         <v>20</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>10</v>
@@ -1444,10 +1483,10 @@
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>10</v>
@@ -1466,7 +1505,7 @@
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>69</v>
@@ -1483,31 +1522,31 @@
         <v>12</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="F55" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="56" spans="1:6" ht="15" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>72</v>
@@ -1515,7 +1554,7 @@
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>73</v>
@@ -1528,52 +1567,34 @@
       <c r="C59" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="F59" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D61" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D62" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E62" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>78</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -1587,33 +1608,42 @@
       <c r="C63" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="D64" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="D65" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F65" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1">
@@ -1623,6 +1653,9 @@
       <c r="C66" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="E66" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F66" s="1" t="s">
         <v>10</v>
       </c>
@@ -1637,29 +1670,35 @@
       <c r="F67" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="G67" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="F69" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="70" spans="1:7" ht="15" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>10</v>
@@ -1667,21 +1706,18 @@
     </row>
     <row r="71" spans="1:7" ht="15" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>10</v>
@@ -1689,18 +1725,21 @@
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>10</v>
@@ -1708,7 +1747,7 @@
     </row>
     <row r="75" spans="1:7" ht="15" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>88</v>
@@ -1716,19 +1755,10 @@
     </row>
     <row r="76" spans="1:7" ht="15" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="D76" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" customHeight="1">
@@ -1736,159 +1766,135 @@
         <v>20</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
+      </c>
+      <c r="D79" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>19</v>
+        <v>94</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="C81" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>102</v>
-      </c>
     </row>
     <row r="83" spans="1:7" ht="15" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>65</v>
+        <v>16</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="85" spans="1:7" ht="15" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>96</v>
-      </c>
     </row>
     <row r="87" spans="1:7" ht="15" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>10</v>
@@ -1896,56 +1902,212 @@
     </row>
     <row r="88" spans="1:7" ht="15" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F89" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="90" spans="1:7" ht="15" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="91" spans="1:7" ht="15" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="92" spans="1:7" ht="15" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F92" s="1" t="s">
+    </row>
+    <row r="93" spans="1:7" ht="15" customHeight="1">
+      <c r="A93" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15" customHeight="1">
+      <c r="A94" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15" customHeight="1">
+      <c r="A95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15" customHeight="1">
+      <c r="A96" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15" customHeight="1">
+      <c r="A97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15" customHeight="1">
+      <c r="A98" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="15" customHeight="1">
+      <c r="A99" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15" customHeight="1">
+      <c r="A100" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="15" customHeight="1">
+      <c r="A101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15" customHeight="1">
+      <c r="A102" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15" customHeight="1">
+      <c r="A103" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="15" customHeight="1">
+      <c r="A104" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15" customHeight="1">
+      <c r="A105" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15" customHeight="1">
+      <c r="A106" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15" customHeight="1">
+      <c r="A107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1962,6 +2124,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="fcd340d3-9f5f-48dd-8d5c-2217be56346f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20023a54-7c36-4e86-bf34-242dee51d4ed">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010055FA13453D9FCF449C164C22E96F7457" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="4e1d86ea8733152a7960a8b70373949e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20023a54-7c36-4e86-bf34-242dee51d4ed" xmlns:ns3="fcd340d3-9f5f-48dd-8d5c-2217be56346f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab7675c617efdd574eaa9783004d1180" ns2:_="" ns3:_="">
     <xsd:import namespace="20023a54-7c36-4e86-bf34-242dee51d4ed"/>
@@ -2162,28 +2344,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="fcd340d3-9f5f-48dd-8d5c-2217be56346f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20023a54-7c36-4e86-bf34-242dee51d4ed">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69EA8DD1-6CEA-4F8B-8084-428D52A152F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3F17D1-1B60-44C4-BBFF-2D75190C1A26}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2191,5 +2353,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3F17D1-1B60-44C4-BBFF-2D75190C1A26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69EA8DD1-6CEA-4F8B-8084-428D52A152F1}"/>
 </file>
--- a/data/RP_Software_Aprobado.xlsx
+++ b/data/RP_Software_Aprobado.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29421"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49252AE1-750B-4DC3-BFCE-F7CFFBF08E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A8182DA-1256-475C-B408-B1EE37CB7B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="136">
   <si>
     <t>Inventario de Software por Rol / Puesto</t>
   </si>
@@ -159,9 +159,18 @@
     <t>CrystalDiskMark</t>
   </si>
   <si>
+    <t>Electronica</t>
+  </si>
+  <si>
+    <t>COMMGR 1.14</t>
+  </si>
+  <si>
     <t>DaVinci Resolve</t>
   </si>
   <si>
+    <t>DobotStudio</t>
+  </si>
+  <si>
     <t>draw.io</t>
   </si>
   <si>
@@ -183,16 +192,19 @@
     <t>DWG FastView</t>
   </si>
   <si>
+    <t>EcoStruxure Machine Expert - Basic V1.2.1.134</t>
+  </si>
+  <si>
+    <t>EPLAN</t>
+  </si>
+  <si>
     <t>Vigilancia</t>
   </si>
   <si>
     <t>Ezviz Studio</t>
   </si>
   <si>
-    <t>Electronica</t>
-  </si>
-  <si>
-    <t>EcoStruxure Machine Expert - Basic</t>
+    <t>Festo Automation Suit</t>
   </si>
   <si>
     <t>Foxit PDF Reader</t>
@@ -204,12 +216,21 @@
     <t>Git</t>
   </si>
   <si>
+    <t>GIMP</t>
+  </si>
+  <si>
     <t>Google Chrome</t>
   </si>
   <si>
     <t>Google Drive</t>
   </si>
   <si>
+    <t>HWCONFIG 4.07</t>
+  </si>
+  <si>
+    <t>HWCONFIG 4.12</t>
+  </si>
+  <si>
     <t>Coordinacion Produccion</t>
   </si>
   <si>
@@ -231,6 +252,9 @@
     <t>Vicrtoria Rothkopf</t>
   </si>
   <si>
+    <t>ISPSoft</t>
+  </si>
+  <si>
     <t>iVMS-4200</t>
   </si>
   <si>
@@ -258,6 +282,12 @@
     <t>Logi Options+</t>
   </si>
   <si>
+    <t>LOGO! Soft Comfort</t>
+  </si>
+  <si>
+    <t>Lightshot-5.5.0.7</t>
+  </si>
+  <si>
     <t>Macrium Reflect</t>
   </si>
   <si>
@@ -345,6 +375,9 @@
     <t>S.I.Ap.</t>
   </si>
   <si>
+    <t>Seclore</t>
+  </si>
+  <si>
     <t>Siemens OPCUA v17</t>
   </si>
   <si>
@@ -354,39 +387,33 @@
     <t>Smart Connect</t>
   </si>
   <si>
-    <t>Seclore</t>
-  </si>
-  <si>
     <t>Spotify</t>
   </si>
   <si>
     <t>Desde Microsoft Store</t>
   </si>
   <si>
-    <t>ISPSoft</t>
-  </si>
-  <si>
     <t>TD Keypad Designer</t>
   </si>
   <si>
+    <t>Tia Portal V16</t>
+  </si>
+  <si>
+    <t>V16</t>
+  </si>
+  <si>
+    <t>Tia Portal V17</t>
+  </si>
+  <si>
+    <t>V17</t>
+  </si>
+  <si>
     <t>TxConfig</t>
   </si>
   <si>
     <t>TxConfig II</t>
   </si>
   <si>
-    <t>Tia Portal V16</t>
-  </si>
-  <si>
-    <t>V16</t>
-  </si>
-  <si>
-    <t>Tia Portal V17</t>
-  </si>
-  <si>
-    <t>V17</t>
-  </si>
-  <si>
     <t>UaExpert</t>
   </si>
   <si>
@@ -396,22 +423,22 @@
     <t>Vijeo Designer</t>
   </si>
   <si>
+    <t>Virtual COM</t>
+  </si>
+  <si>
     <t>Visual Studio Code</t>
   </si>
   <si>
     <t>VLC Media Player</t>
   </si>
   <si>
-    <t>Virtual COM</t>
-  </si>
-  <si>
     <t>WhatsApp</t>
   </si>
   <si>
+    <t>WinRAR</t>
+  </si>
+  <si>
     <t>WorkVisual</t>
-  </si>
-  <si>
-    <t>WinRAR</t>
   </si>
   <si>
     <t>XAMPP</t>
@@ -625,10 +652,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G107" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A2:G107" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G107">
-    <sortCondition ref="C2:C107"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G117" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A2:G117" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G117">
+    <sortCondition ref="C2:C117"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Area / Rol" dataDxfId="6"/>
@@ -819,12 +846,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="37.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.85546875" style="1" customWidth="1"/>
     <col min="4" max="6" width="23.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="94.140625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="8.85546875" style="1"/>
@@ -1147,335 +1174,302 @@
     </row>
     <row r="21" spans="1:7" ht="15.75">
       <c r="A21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75">
       <c r="A22" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1">
+    <row r="23" spans="1:7" ht="15.75">
       <c r="A23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="F24" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="E26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
       <c r="A29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1">
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="C35" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1">
+      <c r="F35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="C36" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15" customHeight="1">
+        <v>57</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1">
+      <c r="F38" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" customHeight="1">
       <c r="A39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1">
+    </row>
+    <row r="40" spans="1:7" ht="15" customHeight="1">
       <c r="A40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1">
+      <c r="F40" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" customHeight="1">
       <c r="A41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1">
+    </row>
+    <row r="42" spans="1:7" ht="15" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E42" s="1" t="s">
+    </row>
+    <row r="43" spans="1:7" ht="15" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="15" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="15" customHeight="1">
+    </row>
+    <row r="44" spans="1:7" ht="15" customHeight="1">
       <c r="A44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" customHeight="1">
+      <c r="A46" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1">
-      <c r="A45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1">
-      <c r="A46" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C46" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1">
+    </row>
+    <row r="48" spans="1:7" ht="15" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>10</v>
@@ -1483,10 +1477,10 @@
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>10</v>
@@ -1494,43 +1488,37 @@
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>10</v>
@@ -1538,31 +1526,49 @@
     </row>
     <row r="56" spans="1:6" ht="15" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>51</v>
+        <v>23</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>74</v>
@@ -1573,18 +1579,24 @@
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>76</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1">
@@ -1594,36 +1606,27 @@
       <c r="C62" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="F62" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D64" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>10</v>
@@ -1631,19 +1634,10 @@
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D65" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1">
@@ -1651,54 +1645,39 @@
         <v>8</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>10</v>
@@ -1706,28 +1685,28 @@
     </row>
     <row r="71" spans="1:7" ht="15" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>88</v>
       </c>
       <c r="F73" s="1" t="s">
@@ -1736,37 +1715,58 @@
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+      <c r="D75" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="D76" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>10</v>
@@ -1774,86 +1774,62 @@
     </row>
     <row r="78" spans="1:7" ht="15" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D79" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E79" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D80" s="1" t="s">
         <v>95</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>10</v>
@@ -1861,246 +1837,279 @@
     </row>
     <row r="84" spans="1:7" ht="15" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
+      </c>
+      <c r="D90" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>99</v>
+        <v>19</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C96" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15" customHeight="1">
+      <c r="A97" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D96" s="1" t="s">
+    </row>
+    <row r="98" spans="1:7" ht="15" customHeight="1">
+      <c r="A98" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="15" customHeight="1">
-      <c r="A97" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C97" s="1" t="s">
+    <row r="99" spans="1:7" ht="15" customHeight="1">
+      <c r="A99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="15" customHeight="1">
-      <c r="A98" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="15" customHeight="1">
-      <c r="A99" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C99" s="1" t="s">
+      <c r="F99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="15" customHeight="1">
+    <row r="100" spans="1:7" ht="15" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15" customHeight="1">
+    <row r="101" spans="1:7" ht="15" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>120</v>
       </c>
+      <c r="D101" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="F101" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15" customHeight="1">
+    <row r="102" spans="1:7" ht="15" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C102" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="15" customHeight="1">
+    </row>
+    <row r="103" spans="1:7" ht="15" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" ht="15" customHeight="1">
+      <c r="D103" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="15" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C104" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F104" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="15" customHeight="1">
+    </row>
+    <row r="105" spans="1:7" ht="15" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15" customHeight="1">
+    <row r="106" spans="1:7" ht="15" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F106" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="15" customHeight="1">
+    </row>
+    <row r="107" spans="1:7" ht="15" customHeight="1">
       <c r="A107" s="1" t="s">
         <v>20</v>
       </c>
@@ -2108,6 +2117,101 @@
         <v>126</v>
       </c>
       <c r="F107" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15" customHeight="1">
+      <c r="A108" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="15" customHeight="1">
+      <c r="A109" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="15" customHeight="1">
+      <c r="A110" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="15" customHeight="1">
+      <c r="A111" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="15" customHeight="1">
+      <c r="A112" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="15" customHeight="1">
+      <c r="A113" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="15" customHeight="1">
+      <c r="A114" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="15" customHeight="1">
+      <c r="A115" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="15" customHeight="1">
+      <c r="A116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="15" customHeight="1">
+      <c r="A117" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/data/RP_Software_Aprobado.xlsx
+++ b/data/RP_Software_Aprobado.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29421"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A8182DA-1256-475C-B408-B1EE37CB7B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B0B1E33-6D1B-4504-AB57-87FBB08B60D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="139">
   <si>
     <t>Inventario de Software por Rol / Puesto</t>
   </si>
@@ -442,6 +442,15 @@
   </si>
   <si>
     <t>XAMPP</t>
+  </si>
+  <si>
+    <t>FluidSIM Pneumatics V 4.2</t>
+  </si>
+  <si>
+    <t>Comex</t>
+  </si>
+  <si>
+    <t>Ivana Kechchian</t>
   </si>
 </sst>
 </file>
@@ -652,8 +661,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G117" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A2:G117" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G119" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A2:G119" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G117">
     <sortCondition ref="C2:C117"/>
   </sortState>
@@ -846,12 +855,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="37.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="57.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="23.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="94.140625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="8.85546875" style="1"/>
@@ -2212,6 +2221,31 @@
         <v>135</v>
       </c>
       <c r="F117" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="15" customHeight="1">
+      <c r="A118" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="15" customHeight="1">
+      <c r="A119" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/data/RP_Software_Aprobado.xlsx
+++ b/data/RP_Software_Aprobado.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29421"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29429"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B0B1E33-6D1B-4504-AB57-87FBB08B60D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cremonainoxidablesrl.sharepoint.com/Documentos compartidos/DOCUMENTACION_GENERAL/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="615" documentId="11_E78ABCF9914A3A57CBC8CB18E01CC106B4376CF9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7C2B100-EFAB-48D3-9536-EE9B7ADBBA5F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista de Soft" sheetId="1" r:id="rId1"/>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="141">
   <si>
     <t>Inventario de Software por Rol / Puesto</t>
   </si>
@@ -123,9 +128,6 @@
     <t>Gerencia</t>
   </si>
   <si>
-    <t>CA</t>
-  </si>
-  <si>
     <t>Mecanica</t>
   </si>
   <si>
@@ -153,18 +155,18 @@
     <t>Clipchamp</t>
   </si>
   <si>
+    <t>Electronica</t>
+  </si>
+  <si>
+    <t>COMMGR 1.14</t>
+  </si>
+  <si>
     <t>CrystalDiskInfo</t>
   </si>
   <si>
     <t>CrystalDiskMark</t>
   </si>
   <si>
-    <t>Electronica</t>
-  </si>
-  <si>
-    <t>COMMGR 1.14</t>
-  </si>
-  <si>
     <t>DaVinci Resolve</t>
   </si>
   <si>
@@ -207,45 +209,48 @@
     <t>Festo Automation Suit</t>
   </si>
   <si>
+    <t>FluidSIM Pneumatics V 4.2</t>
+  </si>
+  <si>
     <t>Foxit PDF Reader</t>
   </si>
   <si>
     <t>para visualización, edición y batch print de pdf ordenados</t>
   </si>
   <si>
+    <t>GIMP</t>
+  </si>
+  <si>
     <t>Git</t>
   </si>
   <si>
-    <t>GIMP</t>
-  </si>
-  <si>
     <t>Google Chrome</t>
   </si>
   <si>
     <t>Google Drive</t>
   </si>
   <si>
+    <t>Coordinacion Produccion</t>
+  </si>
+  <si>
+    <t>HiLookVision</t>
+  </si>
+  <si>
+    <t>Calidad</t>
+  </si>
+  <si>
+    <t>Expedicion</t>
+  </si>
+  <si>
+    <t>Taller</t>
+  </si>
+  <si>
     <t>HWCONFIG 4.07</t>
   </si>
   <si>
     <t>HWCONFIG 4.12</t>
   </si>
   <si>
-    <t>Coordinacion Produccion</t>
-  </si>
-  <si>
-    <t>HiLookVision</t>
-  </si>
-  <si>
-    <t>Calidad</t>
-  </si>
-  <si>
-    <t>Expedicion</t>
-  </si>
-  <si>
-    <t>Taller</t>
-  </si>
-  <si>
     <t>Inkscape</t>
   </si>
   <si>
@@ -258,6 +263,12 @@
     <t>iVMS-4200</t>
   </si>
   <si>
+    <t>Comex</t>
+  </si>
+  <si>
+    <t>Ivana Kechchian</t>
+  </si>
+  <si>
     <t>IXON VPN</t>
   </si>
   <si>
@@ -279,15 +290,15 @@
     <t>LibreOffice</t>
   </si>
   <si>
+    <t>Lightshot-5.5.0.7</t>
+  </si>
+  <si>
     <t>Logi Options+</t>
   </si>
   <si>
     <t>LOGO! Soft Comfort</t>
   </si>
   <si>
-    <t>Lightshot-5.5.0.7</t>
-  </si>
-  <si>
     <t>Macrium Reflect</t>
   </si>
   <si>
@@ -402,6 +413,9 @@
     <t>V16</t>
   </si>
   <si>
+    <t>Tidal</t>
+  </si>
+  <si>
     <t>Tia Portal V17</t>
   </si>
   <si>
@@ -444,13 +458,10 @@
     <t>XAMPP</t>
   </si>
   <si>
-    <t>FluidSIM Pneumatics V 4.2</t>
-  </si>
-  <si>
-    <t>Comex</t>
-  </si>
-  <si>
-    <t>Ivana Kechchian</t>
+    <t>7-Zip</t>
+  </si>
+  <si>
+    <t>Ubuntu 24.04.1 LTS</t>
   </si>
 </sst>
 </file>
@@ -504,14 +515,16 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -523,6 +536,7 @@
       <font>
         <sz val="12"/>
       </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -542,42 +556,49 @@
         <charset val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="12"/>
       </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="12"/>
       </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="12"/>
       </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="12"/>
       </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="12"/>
       </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="12"/>
       </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="12"/>
       </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -661,10 +682,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G119" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A2:G119" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G117">
-    <sortCondition ref="C2:C117"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G124" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A2:G124" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G118">
+    <sortCondition ref="C2:C118"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Area / Rol" dataDxfId="6"/>
@@ -855,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
@@ -1041,13 +1062,13 @@
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -1061,12 +1082,12 @@
         <v>10</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -1083,7 +1104,7 @@
     </row>
     <row r="14" spans="1:7" s="3" customFormat="1" ht="15.75">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -1097,15 +1118,15 @@
         <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1">
         <v>2022</v>
@@ -1114,15 +1135,15 @@
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75">
       <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="D16" s="1">
         <v>2022</v>
@@ -1131,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75">
@@ -1139,13 +1160,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75">
@@ -1153,7 +1174,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>10</v>
@@ -1161,7 +1182,7 @@
     </row>
     <row r="19" spans="1:7" ht="15.75">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>39</v>
@@ -1183,10 +1204,13 @@
     </row>
     <row r="21" spans="1:7" ht="15.75">
       <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>42</v>
+      <c r="F21" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75">
@@ -1197,7 +1221,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>14</v>
@@ -1208,10 +1232,13 @@
     </row>
     <row r="23" spans="1:7" ht="15.75">
       <c r="A23" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1">
@@ -1219,7 +1246,7 @@
         <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>10</v>
@@ -1233,7 +1260,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>19</v>
@@ -1244,22 +1271,22 @@
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1">
@@ -1267,7 +1294,10 @@
         <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1">
@@ -1275,7 +1305,10 @@
         <v>23</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
@@ -1283,39 +1316,54 @@
         <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1">
       <c r="A32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>55</v>
+      <c r="F32" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1">
@@ -1323,26 +1371,26 @@
         <v>23</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>57</v>
@@ -1350,13 +1398,19 @@
       <c r="F36" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="G36" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1">
@@ -1364,7 +1418,7 @@
         <v>20</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>10</v>
@@ -1375,7 +1429,10 @@
         <v>8</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" customHeight="1">
@@ -1383,7 +1440,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>10</v>
@@ -1391,102 +1448,126 @@
     </row>
     <row r="41" spans="1:7" ht="15" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="F43" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="44" spans="1:7" ht="15" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B44" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>69</v>
+        <v>11</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="F50" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>70</v>
@@ -1497,23 +1578,29 @@
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>73</v>
@@ -1524,10 +1611,16 @@
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>54</v>
+        <v>16</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>73</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>10</v>
@@ -1541,7 +1634,7 @@
         <v>24</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>10</v>
@@ -1549,13 +1642,13 @@
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>10</v>
@@ -1563,13 +1656,13 @@
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>10</v>
@@ -1580,7 +1673,7 @@
         <v>20</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>10</v>
@@ -1588,10 +1681,10 @@
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>10</v>
@@ -1602,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>10</v>
@@ -1613,7 +1706,7 @@
         <v>8</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>10</v>
@@ -1627,15 +1720,18 @@
         <v>12</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>10</v>
@@ -1643,10 +1739,13 @@
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1">
@@ -1654,31 +1753,43 @@
         <v>8</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" customHeight="1">
@@ -1686,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>10</v>
@@ -1697,7 +1808,10 @@
         <v>20</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1">
@@ -1705,7 +1819,10 @@
         <v>20</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1">
@@ -1713,10 +1830,10 @@
         <v>8</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>10</v>
@@ -1727,7 +1844,10 @@
         <v>8</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" customHeight="1">
@@ -1738,7 +1858,7 @@
         <v>26</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D75" s="1">
         <v>2021</v>
@@ -1755,13 +1875,13 @@
         <v>11</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D76" s="1">
         <v>2021</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>10</v>
@@ -1772,7 +1892,7 @@
         <v>8</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>19</v>
@@ -1786,21 +1906,24 @@
         <v>20</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" customHeight="1">
@@ -1808,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>10</v>
@@ -1819,7 +1942,7 @@
         <v>20</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>10</v>
@@ -1830,15 +1953,18 @@
         <v>8</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>10</v>
@@ -1849,7 +1975,7 @@
         <v>20</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>10</v>
@@ -1860,7 +1986,7 @@
         <v>11</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>10</v>
@@ -1868,10 +1994,13 @@
     </row>
     <row r="86" spans="1:7" ht="15" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15" customHeight="1">
@@ -1879,7 +2008,10 @@
         <v>8</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15" customHeight="1">
@@ -1887,7 +2019,7 @@
         <v>20</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>10</v>
@@ -1898,21 +2030,24 @@
         <v>8</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D90" s="1">
         <v>2021</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>10</v>
@@ -1923,36 +2058,36 @@
         <v>20</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" customHeight="1">
@@ -1960,7 +2095,10 @@
         <v>20</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" customHeight="1">
@@ -1971,7 +2109,7 @@
         <v>17</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>19</v>
@@ -1988,7 +2126,7 @@
         <v>17</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>19</v>
@@ -1999,18 +2137,24 @@
     </row>
     <row r="96" spans="1:7" ht="15" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" customHeight="1">
@@ -2018,7 +2162,10 @@
         <v>8</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" customHeight="1">
@@ -2026,38 +2173,41 @@
         <v>8</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>10</v>
@@ -2065,65 +2215,77 @@
     </row>
     <row r="102" spans="1:7" ht="15" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>10</v>
@@ -2131,42 +2293,54 @@
     </row>
     <row r="108" spans="1:7" ht="15" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>10</v>
@@ -2174,10 +2348,10 @@
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>10</v>
@@ -2188,7 +2362,7 @@
         <v>8</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>10</v>
@@ -2199,7 +2373,7 @@
         <v>8</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>10</v>
@@ -2207,46 +2381,76 @@
     </row>
     <row r="116" spans="1:6" ht="15" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" customHeight="1">
       <c r="A117" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="15.75">
+      <c r="A118" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="15" customHeight="1">
-      <c r="A118" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C118" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="15" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>137</v>
+        <v>8</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="15" customHeight="1">
+      <c r="A120" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="15" customHeight="1">
+      <c r="A121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="15" customHeight="1">
+      <c r="A122" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2262,15 +2466,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="fcd340d3-9f5f-48dd-8d5c-2217be56346f" xsi:nil="true"/>
@@ -2281,9 +2476,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010055FA13453D9FCF449C164C22E96F7457" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="4e1d86ea8733152a7960a8b70373949e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20023a54-7c36-4e86-bf34-242dee51d4ed" xmlns:ns3="fcd340d3-9f5f-48dd-8d5c-2217be56346f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab7675c617efdd574eaa9783004d1180" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010055FA13453D9FCF449C164C22E96F7457" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1dafc13ea4a753aec82541dfa9be9feb">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20023a54-7c36-4e86-bf34-242dee51d4ed" xmlns:ns3="fcd340d3-9f5f-48dd-8d5c-2217be56346f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89136276e0c5ebeda550c3155f3b8869" ns2:_="" ns3:_="">
     <xsd:import namespace="20023a54-7c36-4e86-bf34-242dee51d4ed"/>
     <xsd:import namespace="fcd340d3-9f5f-48dd-8d5c-2217be56346f"/>
     <xsd:element name="properties">
@@ -2482,14 +2677,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3F17D1-1B60-44C4-BBFF-2D75190C1A26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BB56739-8178-49D0-BAD8-B865A7EB90D2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BB56739-8178-49D0-BAD8-B865A7EB90D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A7F4F-7254-4D1A-AE9D-94448B6CFD36}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69EA8DD1-6CEA-4F8B-8084-428D52A152F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3F17D1-1B60-44C4-BBFF-2D75190C1A26}"/>
 </file>
--- a/data/RP_Software_Aprobado.xlsx
+++ b/data/RP_Software_Aprobado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cremonainoxidablesrl.sharepoint.com/Documentos compartidos/DOCUMENTACION_GENERAL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="615" documentId="11_E78ABCF9914A3A57CBC8CB18E01CC106B4376CF9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7C2B100-EFAB-48D3-9536-EE9B7ADBBA5F}"/>
+  <xr:revisionPtr revIDLastSave="629" documentId="11_E78ABCF9914A3A57CBC8CB18E01CC106B4376CF9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99D9F0FF-BBDF-4B5F-88DF-ECA5F4509F66}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="141">
   <si>
     <t>Inventario de Software por Rol / Puesto</t>
   </si>
@@ -131,7 +131,7 @@
     <t>Mecanica</t>
   </si>
   <si>
-    <t>Exclusividad Windows 10, realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación. Luego de instalación NO ejecutar, llamar a usuario de Sistemas.</t>
+    <t>Exclusividad Windows 10, realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación.</t>
   </si>
   <si>
     <t>Mantenimiento</t>
@@ -143,7 +143,7 @@
     <t>AutoDesk Inventor 2022</t>
   </si>
   <si>
-    <t>Realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación. Luego de instalación NO ejecutar, llamar a usuario de Sistemas.</t>
+    <t>Realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación.</t>
   </si>
   <si>
     <t>Brave</t>
@@ -332,6 +332,12 @@
     <t>Instalar version full.</t>
   </si>
   <si>
+    <t>Lider Proyecto</t>
+  </si>
+  <si>
+    <t>Fernando Russo</t>
+  </si>
+  <si>
     <t>NiceLabel</t>
   </si>
   <si>
@@ -368,13 +374,7 @@
     <t>Descargar desde Microsoft Store</t>
   </si>
   <si>
-    <t>Lider Proyecto</t>
-  </si>
-  <si>
     <t>Reflect</t>
-  </si>
-  <si>
-    <t>Fernando Russo</t>
   </si>
   <si>
     <t>Software de Backup de computadora</t>
@@ -682,10 +682,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G124" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A2:G124" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G118">
-    <sortCondition ref="C2:C118"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G126" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A2:G126" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G120">
+    <sortCondition ref="C2:C120"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Area / Rol" dataDxfId="6"/>
@@ -876,14 +876,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="37.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="23.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="94.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="184.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
@@ -1917,7 +1917,7 @@
     </row>
     <row r="79" spans="1:7" ht="15" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>95</v>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="80" spans="1:7" ht="15" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>10</v>
@@ -1939,9 +1939,15 @@
     </row>
     <row r="81" spans="1:7" ht="15" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C81" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>98</v>
       </c>
       <c r="F81" s="1" t="s">
@@ -1961,7 +1967,7 @@
     </row>
     <row r="83" spans="1:7" ht="15" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>100</v>
@@ -1972,10 +1978,10 @@
     </row>
     <row r="84" spans="1:7" ht="15" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>10</v>
@@ -1983,10 +1989,10 @@
     </row>
     <row r="85" spans="1:7" ht="15" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>10</v>
@@ -1994,10 +2000,10 @@
     </row>
     <row r="86" spans="1:7" ht="15" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>10</v>
@@ -2005,10 +2011,10 @@
     </row>
     <row r="87" spans="1:7" ht="15" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>10</v>
@@ -2016,7 +2022,7 @@
     </row>
     <row r="88" spans="1:7" ht="15" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>102</v>
@@ -2038,56 +2044,41 @@
     </row>
     <row r="90" spans="1:7" ht="15" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D90" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="F90" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
+      </c>
+      <c r="D92" s="1">
+        <v>2021</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" customHeight="1">
@@ -2095,41 +2086,44 @@
         <v>20</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>10</v>
@@ -2137,10 +2131,16 @@
     </row>
     <row r="96" spans="1:7" ht="15" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>10</v>
@@ -2148,10 +2148,16 @@
     </row>
     <row r="97" spans="1:7" ht="15" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>10</v>
@@ -2159,10 +2165,10 @@
     </row>
     <row r="98" spans="1:7" ht="15" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>10</v>
@@ -2170,24 +2176,21 @@
     </row>
     <row r="99" spans="1:7" ht="15" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>10</v>
@@ -2195,22 +2198,16 @@
     </row>
     <row r="101" spans="1:7" ht="15" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" customHeight="1">
@@ -2218,10 +2215,7 @@
         <v>38</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>10</v>
@@ -2229,27 +2223,33 @@
     </row>
     <row r="103" spans="1:7" ht="15" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>10</v>
@@ -2257,24 +2257,27 @@
     </row>
     <row r="105" spans="1:7" ht="15" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>10</v>
@@ -2285,7 +2288,10 @@
         <v>38</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>10</v>
@@ -2293,10 +2299,10 @@
     </row>
     <row r="108" spans="1:7" ht="15" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>10</v>
@@ -2307,7 +2313,7 @@
         <v>38</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>10</v>
@@ -2315,10 +2321,10 @@
     </row>
     <row r="110" spans="1:7" ht="15" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>10</v>
@@ -2329,7 +2335,7 @@
         <v>38</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>10</v>
@@ -2340,7 +2346,7 @@
         <v>38</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>10</v>
@@ -2348,10 +2354,10 @@
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>10</v>
@@ -2359,10 +2365,10 @@
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>10</v>
@@ -2370,10 +2376,10 @@
     </row>
     <row r="115" spans="1:6" ht="15" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>10</v>
@@ -2384,7 +2390,7 @@
         <v>8</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>10</v>
@@ -2392,32 +2398,32 @@
     </row>
     <row r="117" spans="1:6" ht="15" customHeight="1">
       <c r="A117" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="15" customHeight="1">
+      <c r="A118" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="15.75">
+      <c r="A119" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="15.75">
-      <c r="A118" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="15" customHeight="1">
-      <c r="A119" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>10</v>
@@ -2428,28 +2434,50 @@
         <v>20</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="15" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="15" customHeight="1">
       <c r="A122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="15" customHeight="1">
+      <c r="A123" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="15" customHeight="1">
+      <c r="A124" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C122" s="1" t="s">
+      <c r="B124" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2466,6 +2494,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="fcd340d3-9f5f-48dd-8d5c-2217be56346f" xsi:nil="true"/>
@@ -2476,7 +2513,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010055FA13453D9FCF449C164C22E96F7457" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1dafc13ea4a753aec82541dfa9be9feb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20023a54-7c36-4e86-bf34-242dee51d4ed" xmlns:ns3="fcd340d3-9f5f-48dd-8d5c-2217be56346f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89136276e0c5ebeda550c3155f3b8869" ns2:_="" ns3:_="">
     <xsd:import namespace="20023a54-7c36-4e86-bf34-242dee51d4ed"/>
@@ -2677,23 +2714,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3F17D1-1B60-44C4-BBFF-2D75190C1A26}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BB56739-8178-49D0-BAD8-B865A7EB90D2}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A7F4F-7254-4D1A-AE9D-94448B6CFD36}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3F17D1-1B60-44C4-BBFF-2D75190C1A26}"/>
 </file>
--- a/data/RP_Software_Aprobado.xlsx
+++ b/data/RP_Software_Aprobado.xlsx
@@ -1,36 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29429"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cremonainoxidablesrl.sharepoint.com/Documentos compartidos/DOCUMENTACION_GENERAL/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="629" documentId="11_E78ABCF9914A3A57CBC8CB18E01CC106B4376CF9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99D9F0FF-BBDF-4B5F-88DF-ECA5F4509F66}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Lista de Soft" sheetId="1" r:id="rId1"/>
+    <sheet name="Lista de Soft" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -39,436 +20,439 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="141">
-  <si>
-    <t>Inventario de Software por Rol / Puesto</t>
-  </si>
-  <si>
-    <t>Area / Rol</t>
-  </si>
-  <si>
-    <t>Puesto</t>
-  </si>
-  <si>
-    <t>Software</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Usuario Especifico</t>
-  </si>
-  <si>
-    <t>Empresa</t>
-  </si>
-  <si>
-    <t>Notas / Comentarios</t>
-  </si>
-  <si>
-    <t>General</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="141">
+  <si>
+    <t xml:space="preserve">Inventario de Software por Rol / Puesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area / Rol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usuario Especifico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notas / Comentarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General</t>
   </si>
   <si>
     <t xml:space="preserve">Adobe Acrobat </t>
   </si>
   <si>
-    <t>CR</t>
-  </si>
-  <si>
-    <t>Ventas</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>Adobe Illustrator CC 2015</t>
-  </si>
-  <si>
-    <t>Vicrtoria R</t>
-  </si>
-  <si>
-    <t>Adobe Photoshop CC 2015</t>
-  </si>
-  <si>
-    <t>Administracion CR</t>
-  </si>
-  <si>
-    <t>Coordinacion Administracion CR</t>
-  </si>
-  <si>
-    <t>Alison-Desktop</t>
-  </si>
-  <si>
-    <t>Mariana Galante</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>Angry IP Scanner</t>
-  </si>
-  <si>
-    <t>AnyDesk</t>
-  </si>
-  <si>
-    <t>Electrica</t>
-  </si>
-  <si>
-    <t>Coordinacion Electrica</t>
-  </si>
-  <si>
-    <t>AutoDesk AutoCAD 2022</t>
-  </si>
-  <si>
-    <t>Coordinacion Ventas</t>
-  </si>
-  <si>
-    <t>Adrian Bouquet</t>
-  </si>
-  <si>
-    <t>Gerencia</t>
-  </si>
-  <si>
-    <t>Mecanica</t>
-  </si>
-  <si>
-    <t>Exclusividad Windows 10, realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación.</t>
-  </si>
-  <si>
-    <t>Mantenimiento</t>
-  </si>
-  <si>
-    <t>Produccion</t>
-  </si>
-  <si>
-    <t>AutoDesk Inventor 2022</t>
-  </si>
-  <si>
-    <t>Realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación.</t>
-  </si>
-  <si>
-    <t>Brave</t>
-  </si>
-  <si>
-    <t>Establecer como predeterminado</t>
-  </si>
-  <si>
-    <t>Clipchamp</t>
-  </si>
-  <si>
-    <t>Electronica</t>
-  </si>
-  <si>
-    <t>COMMGR 1.14</t>
-  </si>
-  <si>
-    <t>CrystalDiskInfo</t>
-  </si>
-  <si>
-    <t>CrystalDiskMark</t>
-  </si>
-  <si>
-    <t>DaVinci Resolve</t>
-  </si>
-  <si>
-    <t>DobotStudio</t>
-  </si>
-  <si>
-    <t>draw.io</t>
-  </si>
-  <si>
-    <t>Dropbox</t>
-  </si>
-  <si>
-    <t>Coordinacion Mecanica</t>
-  </si>
-  <si>
-    <t>DropBox</t>
-  </si>
-  <si>
-    <t>Leandro Lacolla</t>
-  </si>
-  <si>
-    <t>Complemento de Explorador de archivos</t>
-  </si>
-  <si>
-    <t>DWG FastView</t>
-  </si>
-  <si>
-    <t>EcoStruxure Machine Expert - Basic V1.2.1.134</t>
-  </si>
-  <si>
-    <t>EPLAN</t>
-  </si>
-  <si>
-    <t>Vigilancia</t>
-  </si>
-  <si>
-    <t>Ezviz Studio</t>
-  </si>
-  <si>
-    <t>Festo Automation Suit</t>
-  </si>
-  <si>
-    <t>FluidSIM Pneumatics V 4.2</t>
-  </si>
-  <si>
-    <t>Foxit PDF Reader</t>
-  </si>
-  <si>
-    <t>para visualización, edición y batch print de pdf ordenados</t>
-  </si>
-  <si>
-    <t>GIMP</t>
-  </si>
-  <si>
-    <t>Git</t>
-  </si>
-  <si>
-    <t>Google Chrome</t>
-  </si>
-  <si>
-    <t>Google Drive</t>
-  </si>
-  <si>
-    <t>Coordinacion Produccion</t>
-  </si>
-  <si>
-    <t>HiLookVision</t>
-  </si>
-  <si>
-    <t>Calidad</t>
-  </si>
-  <si>
-    <t>Expedicion</t>
-  </si>
-  <si>
-    <t>Taller</t>
-  </si>
-  <si>
-    <t>HWCONFIG 4.07</t>
-  </si>
-  <si>
-    <t>HWCONFIG 4.12</t>
-  </si>
-  <si>
-    <t>Inkscape</t>
-  </si>
-  <si>
-    <t>Vicrtoria Rothkopf</t>
-  </si>
-  <si>
-    <t>ISPSoft</t>
-  </si>
-  <si>
-    <t>iVMS-4200</t>
-  </si>
-  <si>
-    <t>Comex</t>
-  </si>
-  <si>
-    <t>Ivana Kechchian</t>
-  </si>
-  <si>
-    <t>IXON VPN</t>
-  </si>
-  <si>
-    <t>Lider de Proyecto</t>
+    <t xml:space="preserve">CR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ventas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adobe Illustrator CC 2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicrtoria R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adobe Photoshop CC 2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administracion CR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinacion Administracion CR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alison-Desktop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariana Galante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistemas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angry IP Scanner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyDesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinacion Electrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AutoDesk AutoCAD 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinacion Ventas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Bouquet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exclusividad Windows 10, realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mantenimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AutoDesk Inventor 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar instalación sin conexión a internet, pausar protección de Kaspersky previo a instalación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Establecer como predeterminado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clipchamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMGR 1.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrystalDiskInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrystalDiskMark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DaVinci Resolve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DobotStudio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">draw.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinacion Mecanica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DropBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leandro Lacolla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complemento de Explorador de archivos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DWG FastView</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EcoStruxure Machine Expert - Basic V1.2.1.134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRHH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ePass2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPLAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vigilancia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezviz Studio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Festo Automation Suit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FluidSIM Pneumatics V 4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foxit PDF Reader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">para visualización, edición y batch print de pdf ordenados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Chrome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinacion Produccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiLookVision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expedicion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HWCONFIG 4.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HWCONFIG 4.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inkscape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicrtoria Rothkopf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISPSoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iVMS-4200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivana Kechchian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IXON VPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lider de Proyecto</t>
   </si>
   <si>
     <t xml:space="preserve">Kaspersky </t>
   </si>
   <si>
-    <t>KeePassXC</t>
-  </si>
-  <si>
-    <t>Krita</t>
-  </si>
-  <si>
-    <t>KUKA Engineering Tools</t>
-  </si>
-  <si>
-    <t>LibreOffice</t>
-  </si>
-  <si>
-    <t>Lightshot-5.5.0.7</t>
-  </si>
-  <si>
-    <t>Logi Options+</t>
-  </si>
-  <si>
-    <t>LOGO! Soft Comfort</t>
-  </si>
-  <si>
-    <t>Macrium Reflect</t>
-  </si>
-  <si>
-    <t>Malwarebytes</t>
-  </si>
-  <si>
-    <t>Medibang Pro Paint</t>
-  </si>
-  <si>
-    <t>Microsoft Office</t>
-  </si>
-  <si>
-    <t>2016 / 2019 / 2021</t>
-  </si>
-  <si>
-    <t>Microsoft OneDrive</t>
-  </si>
-  <si>
-    <t>Microsoft Proyect</t>
-  </si>
-  <si>
-    <t>Franco Raad</t>
-  </si>
-  <si>
-    <t>Mozilla Firefox</t>
-  </si>
-  <si>
-    <t>MySQL</t>
-  </si>
-  <si>
-    <t>Instalar version full.</t>
-  </si>
-  <si>
-    <t>Lider Proyecto</t>
-  </si>
-  <si>
-    <t>Fernando Russo</t>
-  </si>
-  <si>
-    <t>NiceLabel</t>
-  </si>
-  <si>
-    <t>Node.js</t>
-  </si>
-  <si>
-    <t>Notepad++</t>
-  </si>
-  <si>
-    <t>OBS Studio</t>
-  </si>
-  <si>
-    <t>Outlook for Windows</t>
-  </si>
-  <si>
-    <t>Postman</t>
-  </si>
-  <si>
-    <t>PowerToys</t>
-  </si>
-  <si>
-    <t>Proyect Office 2021</t>
-  </si>
-  <si>
-    <t>Mariano Perez</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>3.13 / Reciente</t>
-  </si>
-  <si>
-    <t>Descargar desde Microsoft Store</t>
-  </si>
-  <si>
-    <t>Reflect</t>
-  </si>
-  <si>
-    <t>Software de Backup de computadora</t>
-  </si>
-  <si>
-    <t>Revo Uninstaller</t>
-  </si>
-  <si>
-    <t>S.I.Ap.</t>
-  </si>
-  <si>
-    <t>Seclore</t>
-  </si>
-  <si>
-    <t>Siemens OPCUA v17</t>
-  </si>
-  <si>
-    <t>SIMATIC V17</t>
-  </si>
-  <si>
-    <t>Smart Connect</t>
-  </si>
-  <si>
-    <t>Spotify</t>
-  </si>
-  <si>
-    <t>Desde Microsoft Store</t>
-  </si>
-  <si>
-    <t>TD Keypad Designer</t>
-  </si>
-  <si>
-    <t>Tia Portal V16</t>
-  </si>
-  <si>
-    <t>V16</t>
-  </si>
-  <si>
-    <t>Tidal</t>
-  </si>
-  <si>
-    <t>Tia Portal V17</t>
-  </si>
-  <si>
-    <t>V17</t>
-  </si>
-  <si>
-    <t>TxConfig</t>
-  </si>
-  <si>
-    <t>TxConfig II</t>
-  </si>
-  <si>
-    <t>UaExpert</t>
-  </si>
-  <si>
-    <t>UltraVNC</t>
-  </si>
-  <si>
-    <t>Vijeo Designer</t>
-  </si>
-  <si>
-    <t>Virtual COM</t>
-  </si>
-  <si>
-    <t>Visual Studio Code</t>
-  </si>
-  <si>
-    <t>VLC Media Player</t>
-  </si>
-  <si>
-    <t>WhatsApp</t>
-  </si>
-  <si>
-    <t>WinRAR</t>
-  </si>
-  <si>
-    <t>WorkVisual</t>
-  </si>
-  <si>
-    <t>XAMPP</t>
-  </si>
-  <si>
-    <t>7-Zip</t>
-  </si>
-  <si>
-    <t>Ubuntu 24.04.1 LTS</t>
+    <t xml:space="preserve">Krita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KUKA Engineering Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LibreOffice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightshot-5.5.0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logi Options+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOGO! Soft Comfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malwarebytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medibang Pro Paint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016 / 2019 / 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft OneDrive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Proyect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franco Raad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mozilla Firefox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MySQL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalar version full.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lider Proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernando Russo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NiceLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node.js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notepad++</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS Studio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outlook for Windows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PowerToys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proyect Office 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariano Perez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13 / Reciente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descargar desde Microsoft Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reflect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software de Backup de computadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revo Uninstaller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S.I.Ap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seclore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siemens OPCUA v17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMATIC V17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smart Connect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spotify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde Microsoft Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SmartPSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD Keypad Designer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tia Portal V16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tia Portal V17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TxConfig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TxConfig II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UaExpert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UltraVNC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vijeo Designer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtual COM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visual Studio Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VLC Media Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WinRAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkVisual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XAMPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-Zip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ubuntu 24.04.1 LTS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,7 +461,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -500,7 +499,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -508,100 +507,74 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Hyperlink 1" xfId="20"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="1">
     <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -660,95 +633,75 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A2:G126" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A2:G126" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G120">
-    <sortCondition ref="C2:C120"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A2:G125" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:G125"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Area / Rol" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puesto" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Software" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Version" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Usuario Especifico" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{A04E3767-A789-4454-AE68-44B35CDB195E}" name="Empresa" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Notas / Comentarios" dataDxfId="0"/>
+    <tableColumn id="1" name="Area / Rol"/>
+    <tableColumn id="2" name="Puesto"/>
+    <tableColumn id="3" name="Software"/>
+    <tableColumn id="4" name="Version"/>
+    <tableColumn id="5" name="Usuario Especifico"/>
+    <tableColumn id="6" name="Empresa"/>
+    <tableColumn id="7" name="Notas / Comentarios"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -780,7 +733,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -804,7 +757,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -864,41 +817,42 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G124"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G123"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="23.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="184.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="23.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="184.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="8.88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
-      <c r="A1" s="4" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.75">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -921,18 +875,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -942,7 +896,7 @@
       <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -952,7 +906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -962,7 +916,7 @@
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -972,7 +926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -989,7 +943,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -1000,7 +954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1011,7 +965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1021,14 +975,14 @@
       <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="3" customFormat="1" ht="15.75">
+    <row r="10" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1038,7 +992,7 @@
       <c r="C10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1049,7 +1003,7 @@
       </c>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" s="3" customFormat="1" ht="15.75">
+    <row r="11" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1057,7 +1011,7 @@
       <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="1"/>
@@ -1066,7 +1020,7 @@
       </c>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" s="3" customFormat="1" ht="15.75">
+    <row r="12" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -1074,7 +1028,7 @@
       <c r="C12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="1"/>
@@ -1085,7 +1039,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="3" customFormat="1" ht="15.75">
+    <row r="13" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -1093,7 +1047,7 @@
       <c r="C13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="1"/>
@@ -1102,7 +1056,7 @@
       </c>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" s="3" customFormat="1" ht="15.75">
+    <row r="14" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -1110,7 +1064,7 @@
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="1"/>
@@ -1121,14 +1075,14 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1138,14 +1092,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1155,7 +1109,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
@@ -1169,7 +1123,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
@@ -1180,7 +1134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>38</v>
       </c>
@@ -1191,7 +1145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -1202,7 +1156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1213,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>11</v>
       </c>
@@ -1230,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
@@ -1241,7 +1195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>8</v>
       </c>
@@ -1252,7 +1206,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
@@ -1269,7 +1223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" customHeight="1">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1289,7 +1243,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
@@ -1300,7 +1254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1311,7 +1265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>11</v>
       </c>
@@ -1322,7 +1276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -1333,20 +1287,20 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>54</v>
@@ -1355,54 +1309,51 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1">
-      <c r="A34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1">
-      <c r="A35" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="C36" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15" customHeight="1">
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>8</v>
       </c>
@@ -1412,46 +1363,46 @@
       <c r="F37" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="15" customHeight="1">
+      <c r="G37" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="C39" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" customHeight="1">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>64</v>
@@ -1460,125 +1411,128 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" customHeight="1">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>53</v>
+        <v>32</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" customHeight="1">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15" customHeight="1">
-      <c r="A44" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="C44" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="F45" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1">
-      <c r="A50" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1">
-      <c r="A51" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1">
-      <c r="A52" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>72</v>
@@ -1587,112 +1541,112 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1">
-      <c r="A54" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C54" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15" customHeight="1">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="B56" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15" customHeight="1">
-      <c r="A56" s="1" t="s">
+      <c r="E56" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15" customHeight="1">
-      <c r="A57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C57" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15" customHeight="1">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15" customHeight="1">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1">
-      <c r="A60" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15" customHeight="1">
-      <c r="A61" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>78</v>
@@ -1701,18 +1655,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15" customHeight="1">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15" customHeight="1">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>11</v>
       </c>
@@ -1720,190 +1674,193 @@
         <v>12</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15" customHeight="1">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15" customHeight="1">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15" customHeight="1">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15" customHeight="1">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15" customHeight="1">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15" customHeight="1">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15" customHeight="1">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15" customHeight="1">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15" customHeight="1">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15" customHeight="1">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="1" t="n">
         <v>2021</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15" customHeight="1">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D76" s="1">
-        <v>2021</v>
+        <v>94</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15" customHeight="1">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="15" customHeight="1">
+      <c r="G77" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>95</v>
@@ -1911,13 +1868,10 @@
       <c r="F78" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15" customHeight="1">
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>95</v>
@@ -1926,70 +1880,70 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15" customHeight="1">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="E80" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="F80" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15" customHeight="1">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15" customHeight="1">
-      <c r="A82" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15" customHeight="1">
-      <c r="A83" s="1" t="s">
+      <c r="C84" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="15" customHeight="1">
-      <c r="A84" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="15" customHeight="1">
-      <c r="A85" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>102</v>
@@ -1998,9 +1952,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15" customHeight="1">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>102</v>
@@ -2009,9 +1963,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15" customHeight="1">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>102</v>
@@ -2020,116 +1974,122 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15" customHeight="1">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15" customHeight="1">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="15" customHeight="1">
-      <c r="A90" s="1" t="s">
+      <c r="C90" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="15" customHeight="1">
-      <c r="A91" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="15" customHeight="1">
-      <c r="A92" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C92" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D92" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="15" customHeight="1">
+      <c r="G92" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="15" customHeight="1">
-      <c r="A94" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="C94" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G94" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="15" customHeight="1">
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15" customHeight="1">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
         <v>16</v>
       </c>
@@ -2137,7 +2097,7 @@
         <v>17</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>19</v>
@@ -2146,73 +2106,67 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15" customHeight="1">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15" customHeight="1">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15" customHeight="1">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15" customHeight="1">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="15" customHeight="1">
+      <c r="G100" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="15" customHeight="1">
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>121</v>
@@ -2221,49 +2175,52 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15" customHeight="1">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="F103" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="D104" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F103" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="15" customHeight="1">
-      <c r="A104" s="1" t="s">
+      <c r="F104" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D104" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F104" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="15" customHeight="1">
-      <c r="A105" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="15" customHeight="1">
+      <c r="F105" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
         <v>29</v>
       </c>
@@ -2283,7 +2240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="15" customHeight="1">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
         <v>38</v>
       </c>
@@ -2297,7 +2254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15" customHeight="1">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
         <v>38</v>
       </c>
@@ -2308,7 +2265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15" customHeight="1">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
         <v>38</v>
       </c>
@@ -2319,7 +2276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="15" customHeight="1">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
         <v>20</v>
       </c>
@@ -2330,7 +2287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="15" customHeight="1">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
         <v>38</v>
       </c>
@@ -2341,7 +2298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15" customHeight="1">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
         <v>38</v>
       </c>
@@ -2352,7 +2309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="15" customHeight="1">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>38</v>
       </c>
@@ -2363,7 +2320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="15" customHeight="1">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
         <v>38</v>
       </c>
@@ -2374,7 +2331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="15" customHeight="1">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
         <v>20</v>
       </c>
@@ -2385,7 +2342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15" customHeight="1">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>8</v>
       </c>
@@ -2396,7 +2353,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="15" customHeight="1">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
         <v>8</v>
       </c>
@@ -2407,7 +2364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="15" customHeight="1">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>8</v>
       </c>
@@ -2418,7 +2375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="15.75">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
         <v>38</v>
       </c>
@@ -2429,7 +2386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="15" customHeight="1">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>20</v>
       </c>
@@ -2440,7 +2397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="15" customHeight="1">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>8</v>
       </c>
@@ -2451,7 +2408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="15" customHeight="1">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>20</v>
       </c>
@@ -2459,7 +2416,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="15" customHeight="1">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>11</v>
       </c>
@@ -2467,17 +2424,6 @@
         <v>26</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="15" customHeight="1">
-      <c r="A124" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C124" s="1" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2485,35 +2431,20 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="1">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="fcd340d3-9f5f-48dd-8d5c-2217be56346f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20023a54-7c36-4e86-bf34-242dee51d4ed">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010055FA13453D9FCF449C164C22E96F7457" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1dafc13ea4a753aec82541dfa9be9feb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20023a54-7c36-4e86-bf34-242dee51d4ed" xmlns:ns3="fcd340d3-9f5f-48dd-8d5c-2217be56346f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89136276e0c5ebeda550c3155f3b8869" ns2:_="" ns3:_="">
     <xsd:import namespace="20023a54-7c36-4e86-bf34-242dee51d4ed"/>
@@ -2714,14 +2645,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="fcd340d3-9f5f-48dd-8d5c-2217be56346f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20023a54-7c36-4e86-bf34-242dee51d4ed">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3F17D1-1B60-44C4-BBFF-2D75190C1A26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A7F4F-7254-4D1A-AE9D-94448B6CFD36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="20023a54-7c36-4e86-bf34-242dee51d4ed"/>
+    <ds:schemaRef ds:uri="fcd340d3-9f5f-48dd-8d5c-2217be56346f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BB56739-8178-49D0-BAD8-B865A7EB90D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BB56739-8178-49D0-BAD8-B865A7EB90D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fcd340d3-9f5f-48dd-8d5c-2217be56346f"/>
+    <ds:schemaRef ds:uri="20023a54-7c36-4e86-bf34-242dee51d4ed"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A7F4F-7254-4D1A-AE9D-94448B6CFD36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3F17D1-1B60-44C4-BBFF-2D75190C1A26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/RP_Software_Aprobado.xlsx
+++ b/data/RP_Software_Aprobado.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="160">
   <si>
     <t xml:space="preserve">Inventario de Software por Rol / Puesto</t>
   </si>
@@ -109,6 +109,12 @@
     <t xml:space="preserve">AutoDesk AutoCAD 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">Coordinacion Ventas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Bouquet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gerencia</t>
   </si>
   <si>
@@ -124,12 +130,6 @@
     <t xml:space="preserve">Produccion</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinacion Ventas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adrian Bouquet</t>
-  </si>
-  <si>
     <t xml:space="preserve">AutoDesk Inventor 2022</t>
   </si>
   <si>
@@ -154,6 +154,15 @@
     <t xml:space="preserve">CPU-Z</t>
   </si>
   <si>
+    <t xml:space="preserve">ComEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CyptoIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivana Kechchian</t>
+  </si>
+  <si>
     <t xml:space="preserve">CrystalDiskInfo</t>
   </si>
   <si>
@@ -172,12 +181,12 @@
     <t xml:space="preserve">Dropbox</t>
   </si>
   <si>
+    <t xml:space="preserve">Coordinacion Mecanica</t>
+  </si>
+  <si>
     <t xml:space="preserve">DropBox</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinacion Mecanica</t>
-  </si>
-  <si>
     <t xml:space="preserve">Leandro Lacolla</t>
   </si>
   <si>
@@ -205,12 +214,12 @@
     <t xml:space="preserve">Ezviz Studio</t>
   </si>
   <si>
+    <t xml:space="preserve">Lider de Proyecto</t>
+  </si>
+  <si>
     <t xml:space="preserve">Festo Automation Suit</t>
   </si>
   <si>
-    <t xml:space="preserve">Lider de Proyecto</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fernando Russo</t>
   </si>
   <si>
@@ -223,6 +232,9 @@
     <t xml:space="preserve">para visualización, edición y batch print de pdf ordenados</t>
   </si>
   <si>
+    <t xml:space="preserve">GenHash </t>
+  </si>
+  <si>
     <t xml:space="preserve">GIMP</t>
   </si>
   <si>
@@ -241,18 +253,18 @@
     <t xml:space="preserve">HD Tune 2.55</t>
   </si>
   <si>
+    <t xml:space="preserve">Coordinacion Produccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiLookVision</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calidad</t>
   </si>
   <si>
-    <t xml:space="preserve">HiLookVision</t>
-  </si>
-  <si>
     <t xml:space="preserve">Expedicion</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinacion Produccion</t>
-  </si>
-  <si>
     <t xml:space="preserve">Taller</t>
   </si>
   <si>
@@ -274,15 +286,9 @@
     <t xml:space="preserve">Guillermo Gomez</t>
   </si>
   <si>
-    <t xml:space="preserve">ComEx</t>
-  </si>
-  <si>
     <t xml:space="preserve">iVMS-4200</t>
   </si>
   <si>
-    <t xml:space="preserve">Ivana Kechchian</t>
-  </si>
-  <si>
     <t xml:space="preserve">IXON VPN</t>
   </si>
   <si>
@@ -379,18 +385,24 @@
     <t xml:space="preserve">Revo Uninstaller</t>
   </si>
   <si>
+    <t xml:space="preserve">Seclore</t>
+  </si>
+  <si>
     <t xml:space="preserve">S.I.Ap.</t>
   </si>
   <si>
     <t xml:space="preserve">SICORE</t>
   </si>
   <si>
+    <t xml:space="preserve">Slack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siemens OPCUA V17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Siemens OPCUA v17</t>
   </si>
   <si>
-    <t xml:space="preserve">Siemens OPCUA V17</t>
-  </si>
-  <si>
     <t xml:space="preserve">Siemens TIA Portal V17</t>
   </si>
   <si>
@@ -433,6 +445,9 @@
     <t xml:space="preserve">TreeSize</t>
   </si>
   <si>
+    <t xml:space="preserve">TIDAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">TxConfig</t>
   </si>
   <si>
@@ -476,6 +491,12 @@
   </si>
   <si>
     <t xml:space="preserve">WorkVisual 6.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zen Browser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iTunes</t>
   </si>
   <si>
     <t xml:space="preserve">XAMPP</t>
@@ -578,25 +599,21 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -690,8 +707,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A2:G145" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A2:G145"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A2:G153" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:G153"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Area / Rol"/>
     <tableColumn id="2" name="Puesto"/>
@@ -881,15 +898,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
-  <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G154"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="23.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="184.29"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="115.92"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1047,7 +1066,7 @@
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -1062,7 +1081,7 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
@@ -1077,7 +1096,7 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>26</v>
       </c>
@@ -1096,26 +1115,30 @@
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="F13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
@@ -1132,7 +1155,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
@@ -1145,9 +1168,7 @@
       <c r="F15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -1165,33 +1186,31 @@
         <v>10</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>34</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
@@ -1210,7 +1229,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
@@ -1289,16 +1308,20 @@
       </c>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="C24" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="E24" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="F24" s="3" t="s">
         <v>10</v>
       </c>
@@ -1310,7 +1333,7 @@
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1321,18 +1344,14 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B26" s="3"/>
       <c r="C26" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
         <v>10</v>
       </c>
@@ -1340,14 +1359,18 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="C27" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="E27" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="F27" s="3" t="s">
         <v>10</v>
       </c>
@@ -1355,11 +1378,11 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1370,18 +1393,14 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
         <v>10</v>
       </c>
@@ -1389,14 +1408,18 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C30" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="E30" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F30" s="3" t="s">
         <v>10</v>
       </c>
@@ -1404,28 +1427,28 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
@@ -1440,11 +1463,11 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1455,11 +1478,11 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -1470,18 +1493,14 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>51</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D35" s="3"/>
-      <c r="E35" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
         <v>10</v>
       </c>
@@ -1489,14 +1508,18 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="C36" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
+      <c r="E36" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="F36" s="3" t="s">
         <v>10</v>
       </c>
@@ -1504,24 +1527,26 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+      <c r="F37" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -1532,11 +1557,11 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -1547,11 +1572,11 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -1562,11 +1587,11 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -1577,14 +1602,18 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C42" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
+      <c r="E42" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F42" s="3" t="s">
         <v>10</v>
       </c>
@@ -1592,18 +1621,14 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B43" s="3"/>
       <c r="C43" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D43" s="3"/>
-      <c r="E43" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
         <v>10</v>
       </c>
@@ -1611,11 +1636,11 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -1626,20 +1651,18 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="G45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
@@ -1647,7 +1670,7 @@
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -1655,16 +1678,18 @@
         <v>10</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C47" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -1679,22 +1704,24 @@
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G48" s="3"/>
+      <c r="G48" s="3" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -1705,24 +1732,26 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
+      <c r="F50" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -1733,11 +1762,11 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -1748,13 +1777,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -1765,11 +1794,11 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -1780,11 +1809,11 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -1795,11 +1824,11 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -1810,7 +1839,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3" t="s">
@@ -1825,11 +1854,11 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -1840,11 +1869,11 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -1855,11 +1884,11 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -1876,11 +1905,11 @@
         <v>13</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>10</v>
@@ -1889,18 +1918,14 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>27</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B62" s="3"/>
       <c r="C62" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D62" s="3"/>
-      <c r="E62" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
         <v>10</v>
       </c>
@@ -1908,11 +1933,11 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -1923,17 +1948,17 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>10</v>
@@ -1942,11 +1967,11 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -1957,14 +1982,18 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B66" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="C66" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
+      <c r="E66" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="F66" s="3" t="s">
         <v>10</v>
       </c>
@@ -1972,13 +2001,11 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>27</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B67" s="3"/>
       <c r="C67" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -1989,11 +2016,11 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -2004,13 +2031,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -2021,18 +2048,16 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D70" s="3"/>
-      <c r="E70" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
         <v>10</v>
       </c>
@@ -2040,14 +2065,18 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B71" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C71" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
+      <c r="E71" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F71" s="3" t="s">
         <v>10</v>
       </c>
@@ -2055,11 +2084,11 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -2070,7 +2099,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3" t="s">
@@ -2085,7 +2114,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3" t="s">
@@ -2100,13 +2129,11 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B75" s="3"/>
       <c r="C75" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -2117,11 +2144,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="C76" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -2132,18 +2161,14 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B77" s="3"/>
       <c r="C77" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D77" s="3"/>
-      <c r="E77" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
         <v>10</v>
       </c>
@@ -2151,14 +2176,18 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B78" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C78" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
+      <c r="E78" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F78" s="3" t="s">
         <v>10</v>
       </c>
@@ -2219,12 +2248,14 @@
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="3" t="s">
@@ -2239,7 +2270,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3" t="s">
@@ -2254,15 +2285,13 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>100</v>
-      </c>
+      <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
         <v>10</v>
@@ -2271,11 +2300,11 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -2290,12 +2319,12 @@
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
         <v>10</v>
       </c>
@@ -2303,7 +2332,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3" t="s">
@@ -2318,14 +2347,16 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
+      <c r="E89" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F89" s="3" t="s">
         <v>10</v>
       </c>
@@ -2333,17 +2364,17 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>10</v>
@@ -2352,24 +2383,22 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>104</v>
-      </c>
+      <c r="G91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3" t="s">
@@ -2388,14 +2417,16 @@
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
@@ -2414,7 +2445,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3" t="s">
@@ -2429,11 +2460,11 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -2444,11 +2475,11 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -2459,11 +2490,11 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -2474,11 +2505,11 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -2489,7 +2520,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3" t="s">
@@ -2519,18 +2550,14 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>51</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B102" s="3"/>
       <c r="C102" s="3" t="s">
         <v>112</v>
       </c>
       <c r="D102" s="3"/>
-      <c r="E102" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
         <v>10</v>
       </c>
@@ -2538,15 +2565,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D103" s="3" t="n">
-        <v>2021</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="D103" s="3"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3" t="s">
         <v>10</v>
@@ -2555,16 +2580,18 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B104" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="C104" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="E104" s="3"/>
+        <v>114</v>
+      </c>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="F104" s="3" t="s">
         <v>10</v>
       </c>
@@ -2572,43 +2599,37 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D105" s="3" t="s">
         <v>114</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>2021</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G105" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="G105" s="3"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B106" s="3"/>
       <c r="C106" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3" t="s">
-        <v>63</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E106" s="3"/>
       <c r="F106" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G106" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="G106" s="3"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
@@ -2616,48 +2637,50 @@
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D107" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G107" s="3"/>
+      <c r="G107" s="3" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="3" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G108" s="3"/>
+      <c r="G108" s="3" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B109" s="3"/>
       <c r="C109" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D109" s="3"/>
-      <c r="E109" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
         <v>10</v>
       </c>
@@ -2665,14 +2688,18 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B110" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C110" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
+      <c r="E110" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F110" s="3" t="s">
         <v>10</v>
       </c>
@@ -2680,17 +2707,17 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>122</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="3" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>10</v>
@@ -2699,17 +2726,17 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>123</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="3" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>10</v>
@@ -2718,18 +2745,14 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B113" s="3"/>
       <c r="C113" s="3" t="s">
         <v>124</v>
       </c>
       <c r="D113" s="3"/>
-      <c r="E113" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="E113" s="3"/>
       <c r="F113" s="3" t="s">
         <v>10</v>
       </c>
@@ -2737,14 +2760,18 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B114" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C114" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
+      <c r="E114" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F114" s="3" t="s">
         <v>10</v>
       </c>
@@ -2752,18 +2779,14 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B115" s="3"/>
       <c r="C115" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D115" s="3"/>
-      <c r="E115" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="E115" s="3"/>
       <c r="F115" s="3" t="s">
         <v>10</v>
       </c>
@@ -2771,14 +2794,18 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B116" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C116" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
+      <c r="E116" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F116" s="3" t="s">
         <v>10</v>
       </c>
@@ -2786,17 +2813,21 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
+      <c r="E117" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G117" s="3"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2804,27 +2835,33 @@
         <v>33</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
+      <c r="E118" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G118" s="3"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
+      <c r="F119" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G119" s="3"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2833,31 +2870,27 @@
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G120" s="3" t="s">
-        <v>129</v>
-      </c>
+      <c r="G120" s="3"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D121" s="3"/>
-      <c r="E121" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="E121" s="3"/>
       <c r="F121" s="3" t="s">
         <v>10</v>
       </c>
@@ -2865,9 +2898,11 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B122" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="C122" s="3" t="s">
         <v>131</v>
       </c>
@@ -2880,15 +2915,13 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>133</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D123" s="3"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3" t="s">
         <v>10</v>
@@ -2897,37 +2930,35 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B124" s="3"/>
       <c r="C124" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G124" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E124" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G124" s="3"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B125" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C125" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D125" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F125" s="3" t="s">
         <v>10</v>
       </c>
@@ -2935,20 +2966,14 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B126" s="3"/>
       <c r="C126" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D126" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E126" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
       <c r="F126" s="3" t="s">
         <v>10</v>
       </c>
@@ -2956,15 +2981,23 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B127" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C127" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
+      <c r="D127" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G127" s="3"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2973,9 +3006,11 @@
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D128" s="3"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3" t="s">
         <v>10</v>
@@ -2984,28 +3019,36 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B129" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C129" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
+      <c r="D129" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F129" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G129" s="3"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B130" s="3"/>
       <c r="C130" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D130" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D130" s="3"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3" t="s">
         <v>10</v>
@@ -3018,7 +3061,7 @@
       </c>
       <c r="B131" s="3"/>
       <c r="C131" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -3029,30 +3072,32 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
-      <c r="F132" s="3"/>
+      <c r="F132" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G132" s="3"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>34</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B133" s="3"/>
       <c r="C133" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
+      <c r="F133" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G133" s="3"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3061,7 +3106,7 @@
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -3070,20 +3115,16 @@
       </c>
       <c r="G134" s="3"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B135" s="3"/>
       <c r="C135" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D135" s="3"/>
-      <c r="E135" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="E135" s="3"/>
       <c r="F135" s="3" t="s">
         <v>10</v>
       </c>
@@ -3091,11 +3132,11 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -3106,11 +3147,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B137" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="C137" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -3121,18 +3164,14 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B138" s="3"/>
       <c r="C138" s="3" t="s">
         <v>145</v>
       </c>
       <c r="D138" s="3"/>
-      <c r="E138" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="E138" s="3"/>
       <c r="F138" s="3" t="s">
         <v>10</v>
       </c>
@@ -3140,11 +3179,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B139" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C139" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -3155,11 +3196,11 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -3170,14 +3211,18 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B141" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C141" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D141" s="3"/>
-      <c r="E141" s="3"/>
+      <c r="E141" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F141" s="3" t="s">
         <v>10</v>
       </c>
@@ -3185,11 +3230,11 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -3204,7 +3249,7 @@
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -3215,17 +3260,17 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>10</v>
@@ -3238,7 +3283,7 @@
       </c>
       <c r="B145" s="3"/>
       <c r="C145" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -3246,6 +3291,139 @@
         <v>10</v>
       </c>
       <c r="G145" s="3"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" s="3"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" s="3"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G148" s="3"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" s="3"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" s="3"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" s="3"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" s="3"/>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G153" s="3"/>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3485,6 +3663,28 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20023a54-7c36-4e86-bf34-242dee51d4ed">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fcd340d3-9f5f-48dd-8d5c-2217be56346f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20023a54-7c36-4e86-bf34-242dee51d4ed">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fcd340d3-9f5f-48dd-8d5c-2217be56346f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A7F4F-7254-4D1A-AE9D-94448B6CFD36}"/>
 </file>
@@ -3495,4 +3695,12 @@
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3F17D1-1B60-44C4-BBFF-2D75190C1A26}"/>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{647034D8-D67C-4AF3-8E6B-E1C5F34440E1}"/>
+</file>
+
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0FEAA1-E8D2-4DEF-89E5-240B523F1E03}"/>
 </file>
--- a/data/RP_Software_Aprobado.xlsx
+++ b/data/RP_Software_Aprobado.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="163">
   <si>
     <t xml:space="preserve">Inventario de Software por Rol / Puesto</t>
   </si>
@@ -248,6 +248,15 @@
   </si>
   <si>
     <t xml:space="preserve">Google Drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hppM125LaserJetService</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hppM201-M202LaserJetService </t>
+  </si>
+  <si>
+    <t xml:space="preserve">hppcp1025LaserJetService</t>
   </si>
   <si>
     <t xml:space="preserve">HD Tune 2.55</t>
@@ -707,8 +716,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A2:G153" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A2:G153"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A2:G156" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:G156"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Area / Rol"/>
     <tableColumn id="2" name="Puesto"/>
@@ -898,7 +907,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.78"/>
@@ -1762,7 +1771,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
@@ -1770,31 +1779,25 @@
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
-      <c r="F52" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B53" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
-      <c r="F53" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F53" s="3"/>
       <c r="G53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3" t="s">
@@ -1802,18 +1805,16 @@
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -1824,11 +1825,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B56" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="C56" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -1839,11 +1842,11 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -1854,11 +1857,11 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -1869,11 +1872,11 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -1884,11 +1887,11 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -1899,18 +1902,14 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B61" s="3"/>
       <c r="C61" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D61" s="3"/>
-      <c r="E61" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
         <v>10</v>
       </c>
@@ -1918,11 +1917,11 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -1933,11 +1932,11 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -1948,17 +1947,17 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>10</v>
@@ -1967,11 +1966,11 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -1982,18 +1981,14 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>44</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B66" s="3"/>
       <c r="C66" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D66" s="3"/>
-      <c r="E66" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
         <v>10</v>
       </c>
@@ -2001,14 +1996,18 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B67" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="C67" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
+      <c r="E67" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="F67" s="3" t="s">
         <v>10</v>
       </c>
@@ -2016,11 +2015,11 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -2031,16 +2030,18 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
+      <c r="E69" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="F69" s="3" t="s">
         <v>10</v>
       </c>
@@ -2048,13 +2049,11 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B70" s="3"/>
       <c r="C70" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -2065,18 +2064,14 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B71" s="3"/>
       <c r="C71" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D71" s="3"/>
-      <c r="E71" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
         <v>10</v>
       </c>
@@ -2084,11 +2079,13 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="C72" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -2099,11 +2096,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B73" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="C73" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -2114,14 +2113,18 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B74" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C74" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
+      <c r="E74" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F74" s="3" t="s">
         <v>10</v>
       </c>
@@ -2129,11 +2132,11 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -2144,11 +2147,9 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B76" s="3"/>
       <c r="C76" s="3" t="s">
         <v>92</v>
       </c>
@@ -2161,11 +2162,11 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -2176,18 +2177,14 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B78" s="3"/>
       <c r="C78" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D78" s="3"/>
-      <c r="E78" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
         <v>10</v>
       </c>
@@ -2195,11 +2192,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="C79" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -2210,11 +2209,11 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -2225,14 +2224,18 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B81" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C81" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
+      <c r="E81" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F81" s="3" t="s">
         <v>10</v>
       </c>
@@ -2240,7 +2243,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3" t="s">
@@ -2255,7 +2258,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="3" t="s">
@@ -2270,7 +2273,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3" t="s">
@@ -2285,7 +2288,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3" t="s">
@@ -2300,7 +2303,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3" t="s">
@@ -2321,9 +2324,7 @@
       <c r="C87" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>102</v>
-      </c>
+      <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
         <v>10</v>
@@ -2332,11 +2333,11 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -2347,16 +2348,14 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D89" s="3"/>
-      <c r="E89" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
         <v>10</v>
       </c>
@@ -2364,18 +2363,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B90" s="3"/>
       <c r="C90" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
         <v>10</v>
       </c>
@@ -2383,11 +2380,11 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -2398,14 +2395,16 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
+      <c r="E92" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F92" s="3" t="s">
         <v>10</v>
       </c>
@@ -2413,28 +2412,30 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B93" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C93" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
+      <c r="E93" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F93" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G93" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="G93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -2445,7 +2446,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3" t="s">
@@ -2460,22 +2461,24 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3" t="s">
@@ -2490,11 +2493,11 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -2505,11 +2508,11 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -2520,11 +2523,11 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -2535,11 +2538,11 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -2554,7 +2557,7 @@
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -2565,7 +2568,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="3" t="s">
@@ -2580,18 +2583,14 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B104" s="3"/>
       <c r="C104" s="3" t="s">
         <v>114</v>
       </c>
       <c r="D104" s="3"/>
-      <c r="E104" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="E104" s="3"/>
       <c r="F104" s="3" t="s">
         <v>10</v>
       </c>
@@ -2599,15 +2598,13 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D105" s="3" t="n">
-        <v>2021</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D105" s="3"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3" t="s">
         <v>10</v>
@@ -2616,15 +2613,13 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D106" s="3" t="n">
-        <v>2021</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="D106" s="3"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3" t="s">
         <v>10</v>
@@ -2633,53 +2628,51 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B107" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="C107" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E107" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="F107" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G107" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="G107" s="3"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B108" s="3"/>
       <c r="C108" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E108" s="3"/>
       <c r="F108" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G108" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="G108" s="3"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D109" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>2021</v>
+      </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
         <v>10</v>
@@ -2688,56 +2681,54 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B110" s="3"/>
       <c r="C110" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E110" s="3"/>
       <c r="F110" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G110" s="3"/>
+      <c r="G110" s="3" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="3" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G111" s="3"/>
+      <c r="G111" s="3" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B112" s="3"/>
       <c r="C112" s="3" t="s">
         <v>123</v>
       </c>
       <c r="D112" s="3"/>
-      <c r="E112" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E112" s="3"/>
       <c r="F112" s="3" t="s">
         <v>10</v>
       </c>
@@ -2745,14 +2736,18 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B113" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C113" s="3" t="s">
         <v>124</v>
       </c>
       <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
+      <c r="E113" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F113" s="3" t="s">
         <v>10</v>
       </c>
@@ -2760,17 +2755,17 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="3" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>10</v>
@@ -2779,14 +2774,18 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B115" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C115" s="3" t="s">
         <v>126</v>
       </c>
       <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
+      <c r="E115" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F115" s="3" t="s">
         <v>10</v>
       </c>
@@ -2794,18 +2793,14 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B116" s="3"/>
       <c r="C116" s="3" t="s">
         <v>127</v>
       </c>
       <c r="D116" s="3"/>
-      <c r="E116" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="E116" s="3"/>
       <c r="F116" s="3" t="s">
         <v>10</v>
       </c>
@@ -2832,18 +2827,14 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B118" s="3"/>
       <c r="C118" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D118" s="3"/>
-      <c r="E118" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="E118" s="3"/>
       <c r="F118" s="3" t="s">
         <v>10</v>
       </c>
@@ -2851,14 +2842,18 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B119" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C119" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
+      <c r="E119" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F119" s="3" t="s">
         <v>10</v>
       </c>
@@ -2866,14 +2861,18 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B120" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C120" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
+      <c r="E120" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F120" s="3" t="s">
         <v>10</v>
       </c>
@@ -2881,16 +2880,18 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
+      <c r="E121" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F121" s="3" t="s">
         <v>10</v>
       </c>
@@ -2898,13 +2899,11 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>77</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B122" s="3"/>
       <c r="C122" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -2915,11 +2914,11 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -2930,35 +2929,33 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B124" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="C124" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G124" s="3" t="s">
-        <v>133</v>
-      </c>
+      <c r="G124" s="3"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>134</v>
       </c>
       <c r="D125" s="3"/>
-      <c r="E125" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="E125" s="3"/>
       <c r="F125" s="3" t="s">
         <v>10</v>
       </c>
@@ -2966,11 +2963,11 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B126" s="3"/>
       <c r="C126" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -2981,37 +2978,35 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B127" s="3"/>
       <c r="C127" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G127" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G127" s="3"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B128" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C128" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D128" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F128" s="3" t="s">
         <v>10</v>
       </c>
@@ -3019,20 +3014,14 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B129" s="3"/>
       <c r="C129" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
       <c r="F129" s="3" t="s">
         <v>10</v>
       </c>
@@ -3040,16 +3029,20 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B130" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C130" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E130" s="3"/>
+        <v>140</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F130" s="3" t="s">
         <v>10</v>
       </c>
@@ -3057,13 +3050,15 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B131" s="3"/>
       <c r="C131" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D131" s="3"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3" t="s">
         <v>10</v>
@@ -3072,14 +3067,20 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B132" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C132" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D132" s="3"/>
-      <c r="E132" s="3"/>
+      <c r="D132" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F132" s="3" t="s">
         <v>10</v>
       </c>
@@ -3091,9 +3092,11 @@
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D133" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D133" s="3"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3" t="s">
         <v>10</v>
@@ -3102,7 +3105,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3" t="s">
@@ -3115,9 +3118,9 @@
       </c>
       <c r="G134" s="3"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B135" s="3"/>
       <c r="C135" s="3" t="s">
@@ -3132,11 +3135,11 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -3147,13 +3150,11 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>29</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B137" s="3"/>
       <c r="C137" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -3162,13 +3163,13 @@
       </c>
       <c r="G137" s="3"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -3179,13 +3180,11 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B139" s="3"/>
       <c r="C139" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -3196,11 +3195,13 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B140" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="C140" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -3211,18 +3212,14 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B141" s="3"/>
       <c r="C141" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D141" s="3"/>
-      <c r="E141" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="E141" s="3"/>
       <c r="F141" s="3" t="s">
         <v>10</v>
       </c>
@@ -3230,9 +3227,11 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B142" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C142" s="3" t="s">
         <v>148</v>
       </c>
@@ -3279,7 +3278,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B145" s="3"/>
       <c r="C145" s="3" t="s">
@@ -3294,7 +3293,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B146" s="3"/>
       <c r="C146" s="3" t="s">
@@ -3309,14 +3308,18 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B147" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C147" s="3" t="s">
         <v>153</v>
       </c>
       <c r="D147" s="3"/>
-      <c r="E147" s="3"/>
+      <c r="E147" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F147" s="3" t="s">
         <v>10</v>
       </c>
@@ -3324,7 +3327,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B148" s="3"/>
       <c r="C148" s="3" t="s">
@@ -3339,7 +3342,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B149" s="3"/>
       <c r="C149" s="3" t="s">
@@ -3354,18 +3357,14 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B150" s="3"/>
       <c r="C150" s="3" t="s">
         <v>156</v>
       </c>
       <c r="D150" s="3"/>
-      <c r="E150" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="E150" s="3"/>
       <c r="F150" s="3" t="s">
         <v>10</v>
       </c>
@@ -3388,7 +3387,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="3" t="s">
@@ -3403,27 +3402,76 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B153" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C153" s="3" t="s">
         <v>159</v>
       </c>
       <c r="D153" s="3"/>
-      <c r="E153" s="3"/>
+      <c r="E153" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="F153" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G153" s="3"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="3"/>
+      <c r="A154" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B154" s="3"/>
-      <c r="C154" s="3"/>
+      <c r="C154" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
-      <c r="F154" s="3"/>
+      <c r="F154" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G154" s="3"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G155" s="3"/>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G156" s="3"/>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
